--- a/sheets/국악이꽃피는나무/검수/장녹수.xlsx
+++ b/sheets/국악이꽃피는나무/검수/장녹수.xlsx
@@ -5657,50 +5657,43 @@
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="26"/>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="26"/>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O10" s="26"/>
@@ -6170,50 +6163,43 @@
       <c r="C18" s="28"/>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="26"/>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K18" s="26"/>
       <c r="L18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M18" s="26"/>
       <c r="N18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O18" s="26"/>
       <c r="P18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-▽</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q18" s="26"/>

--- a/sheets/국악이꽃피는나무/검수/장녹수.xlsx
+++ b/sheets/국악이꽃피는나무/검수/장녹수.xlsx
@@ -5132,21 +5132,21 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
